--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487060_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487060_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.641</v>
+        <v>8.6302</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8401</v>
+        <v>5.338</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8008</v>
+        <v>3.2922</v>
       </c>
       <c r="G2" t="n">
         <v>5.3595</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2104</v>
+        <v>1.1997</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2078</v>
+        <v>0.7056</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0027</v>
+        <v>0.494</v>
       </c>
       <c r="V2" t="n">
         <v>3.0361</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0172</v>
+        <v>0.8841</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4483</v>
+        <v>1.3496</v>
       </c>
       <c r="F3" t="n">
         <v>-0.4655</v>
@@ -688,10 +688,10 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4151</v>
+        <v>0.4862</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7733</v>
+        <v>0.1279</v>
       </c>
       <c r="U3" t="n">
         <v>0.3582</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3286</v>
+        <v>-0.3682</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.331</v>
+        <v>-0.5313</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0025</v>
+        <v>0.1631</v>
       </c>
       <c r="G4" t="n">
         <v>-1.5799</v>
@@ -766,13 +766,13 @@
         <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0423</v>
+        <v>-0.082</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2512</v>
+        <v>0.0509</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2935</v>
+        <v>-0.1329</v>
       </c>
       <c r="V4" t="n">
         <v>1.2936</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5868</v>
+        <v>-0.5653</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-1.4344</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1657</v>
+        <v>0.869</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1654</v>
+        <v>1.8571</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0598</v>
+        <v>3.2116</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1057</v>
+        <v>-1.3545</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9303</v>
+        <v>2.7114</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3362</v>
+        <v>4.0466</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5941</v>
+        <v>-1.3352</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0957</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.396</v>
+        <v>-0.835</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6998</v>
+        <v>-0.0193</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9301</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q5" t="n">
         <v>-4.8252</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8951</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.963</v>
+        <v>-0.0212</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4429</v>
+        <v>0.0655</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5202</v>
+        <v>-0.0866</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5457</v>
+        <v>0.1079</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6996</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1539</v>
+        <v>-0.5061</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2197</v>
+        <v>-1.2818</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0352</v>
+        <v>-1.153</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8155</v>
+        <v>-0.1288</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8571</v>
+        <v>-1.1654</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2116</v>
+        <v>-1.0598</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3545</v>
+        <v>-0.1057</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7114</v>
+        <v>0.9303</v>
       </c>
       <c r="K6" t="n">
-        <v>4.0466</v>
+        <v>0.3362</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3352</v>
+        <v>0.5941</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-2.0957</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.835</v>
+        <v>-1.396</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0193</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5091</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q6" t="n">
         <v>-4.8252</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3161</v>
+        <v>2.8951</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6755</v>
+        <v>0.268</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5354</v>
+        <v>0.0423</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1402</v>
+        <v>0.2257</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1079</v>
+        <v>1.5457</v>
       </c>
       <c r="W6" t="n">
-        <v>0.614</v>
+        <v>2.6996</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5061</v>
+        <v>-1.1539</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SAN JOSE GONZALEZ</t>
+          <t>G. DE LA CRUZ MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3998</v>
+        <v>-2.5808</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1435</v>
+        <v>-2.958</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2563</v>
+        <v>0.3772</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5749</v>
+        <v>-3.2768</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3539</v>
+        <v>-0.4749</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.221</v>
+        <v>-2.8018</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-1.1548</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.1397</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.2945</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5749</v>
+        <v>-2.1219</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3539</v>
+        <v>-0.6146</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.221</v>
+        <v>-1.5073</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1401</v>
+        <v>-0.3672</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1785</v>
+        <v>-0.2059</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3186</v>
+        <v>-0.1613</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.1862</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.7302999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. DE LA CRUZ MARTINEZ</t>
+          <t>J. SAN JOSE GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5877</v>
+        <v>-2.614</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8578</v>
+        <v>-1.1435</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2701</v>
+        <v>-1.4705</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.2768</v>
+        <v>-1.5749</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4749</v>
+        <v>-0.3539</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8018</v>
+        <v>-1.221</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1548</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1397</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2945</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1219</v>
+        <v>-1.5749</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6146</v>
+        <v>-0.3539</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5073</v>
+        <v>-1.221</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3741</v>
+        <v>-0.074</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1057</v>
+        <v>-0.1785</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2684</v>
+        <v>0.1044</v>
       </c>
       <c r="V8" t="n">
-        <v>3.1862</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7302999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.6533</v>
+        <v>-5.1654</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1765</v>
+        <v>-2.8761</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4767</v>
+        <v>-2.2893</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1178</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3002</v>
+        <v>-0.8124</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6544</v>
+        <v>-0.3539</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6458</v>
+        <v>-0.4584</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8842</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.927199999999999</v>
+        <v>-8.018000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-8.813800000000001</v>
+        <v>-8.4133</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1134</v>
+        <v>0.3952</v>
       </c>
       <c r="G10" t="n">
         <v>-7.1331</v>
@@ -1234,13 +1234,13 @@
         <v>3.6672</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3544</v>
+        <v>-0.4452</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5221</v>
+        <v>-0.1216</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.3236</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8258</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.0793</v>
+        <v>-11.0792</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.8219</v>
+        <v>-11.822</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7427000000000006</v>
+        <v>0.7425999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-8.137</v>
@@ -1300,10 +1300,10 @@
         <v>-5.7788</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.233600000000001</v>
+        <v>-6.2336</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.720299999999999</v>
+        <v>-7.720300000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-26.056</v>
@@ -1312,16 +1312,16 @@
         <v>18.3357</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1518999999999999</v>
+        <v>0.1519</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1325000000000005</v>
+        <v>0.1323</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01959999999999995</v>
+        <v>0.01950000000000007</v>
       </c>
       <c r="V11" t="n">
-        <v>4.626</v>
+        <v>4.625999999999999</v>
       </c>
       <c r="W11" t="n">
         <v>10.2266</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.0798</v>
+        <v>3.7317</v>
       </c>
       <c r="E12" t="n">
         <v>1.3409</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7389</v>
+        <v>2.3909</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6869</v>
@@ -1390,13 +1390,13 @@
         <v>2.1231</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4964</v>
+        <v>0.1484</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2247</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7211</v>
+        <v>0.3731</v>
       </c>
       <c r="V12" t="n">
         <v>3.1122</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4228</v>
+        <v>3.4694</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1375</v>
+        <v>2.2376</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2853</v>
+        <v>1.2318</v>
       </c>
       <c r="G13" t="n">
         <v>4.6937</v>
@@ -1468,13 +1468,13 @@
         <v>3.8602</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6147</v>
+        <v>-0.5681</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4032</v>
+        <v>-0.303</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2115</v>
+        <v>-0.2651</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6562</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2642</v>
+        <v>3.1978</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7382</v>
+        <v>2.5379</v>
       </c>
       <c r="F14" t="n">
-        <v>0.526</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.1313</v>
@@ -1546,13 +1546,13 @@
         <v>1.158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2531</v>
+        <v>-0.3196</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1917</v>
+        <v>-0.0086</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4449</v>
+        <v>-0.311</v>
       </c>
       <c r="V14" t="n">
         <v>1.228</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9435</v>
+        <v>3.133</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5531</v>
+        <v>0.7932</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3903</v>
+        <v>2.3398</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0757</v>
+        <v>2.3284</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6344</v>
+        <v>-1.8215</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4413</v>
+        <v>4.1499</v>
       </c>
       <c r="J15" t="n">
-        <v>1.029</v>
+        <v>1.6678</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9883</v>
+        <v>-0.8798</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0407</v>
+        <v>2.5476</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0466</v>
+        <v>0.6605</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3539</v>
+        <v>-0.9417</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4006</v>
+        <v>1.6022</v>
       </c>
       <c r="P15" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8256</v>
+        <v>-0.2304</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4891</v>
+        <v>-0.1725</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3364</v>
+        <v>-0.0579</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="W15" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.6562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3447</v>
+        <v>2.4557</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1924</v>
+        <v>0.2527</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1524</v>
+        <v>2.203</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3284</v>
+        <v>1.0757</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8215</v>
+        <v>0.6344</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1499</v>
+        <v>0.4413</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6678</v>
+        <v>1.029</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8798</v>
+        <v>0.9883</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5476</v>
+        <v>0.0407</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6605</v>
+        <v>0.0466</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9417</v>
+        <v>-0.3539</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6022</v>
+        <v>0.4006</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0186</v>
+        <v>0.3378</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7733</v>
+        <v>0.1887</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2452</v>
+        <v>0.149</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>0.6562</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1603</v>
+        <v>2.428</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0689</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2292</v>
+        <v>2.4968</v>
       </c>
       <c r="G17" t="n">
         <v>0.8250999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>3.0881</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7879</v>
+        <v>-0.5202</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4627</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3252</v>
+        <v>-0.0575</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3625</v>
+        <v>1.3427</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0217</v>
+        <v>-0.1218</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3842</v>
+        <v>1.4645</v>
       </c>
       <c r="G18" t="n">
         <v>0.125</v>
@@ -1858,13 +1858,13 @@
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3497</v>
+        <v>0.3298</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4297</v>
+        <v>0.3295</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6562</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0251</v>
+        <v>0.9984</v>
       </c>
       <c r="E19" t="n">
         <v>3.882</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8569</v>
+        <v>-2.8836</v>
       </c>
       <c r="G19" t="n">
         <v>4.6283</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1157</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>0.0727</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0429</v>
+        <v>0.0162</v>
       </c>
       <c r="V19" t="n">
         <v>-4.2979</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4787</v>
+        <v>-0.4027</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3159</v>
+        <v>-0.4852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1628</v>
+        <v>0.0825</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0507</v>
@@ -2014,13 +2014,13 @@
         <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5342</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5269</v>
+        <v>0.7258</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0073</v>
+        <v>-0.0731</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1278</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.357</v>
+        <v>-0.7026</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4675</v>
+        <v>-3.8667</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1105</v>
+        <v>3.1641</v>
       </c>
       <c r="G21" t="n">
         <v>0.09229999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>3.2811</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1719</v>
+        <v>0.4825</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5354</v>
+        <v>0.0655</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3635</v>
+        <v>0.4171</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6985</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0766</v>
+        <v>-3.5026</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3094</v>
+        <v>-3.7085</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2327</v>
+        <v>0.206</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1319</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0569</v>
+        <v>-0.4828</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8328</v>
+        <v>-0.232</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2241</v>
+        <v>-0.2509</v>
       </c>
       <c r="V22" t="n">
         <v>0.0422</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5686</v>
+        <v>-5.0693</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0351</v>
+        <v>-3.5358</v>
       </c>
       <c r="F23" t="n">
         <v>-1.5335</v>
@@ -2248,10 +2248,10 @@
         <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4297</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5024</v>
+        <v>0.0017</v>
       </c>
       <c r="U23" t="n">
         <v>-0.0727</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>11.0794</v>
+        <v>11.0795</v>
       </c>
       <c r="E24" t="n">
         <v>-0.7426000000000004</v>
       </c>
       <c r="F24" t="n">
-        <v>11.8219</v>
+        <v>11.8221</v>
       </c>
       <c r="G24" t="n">
         <v>8.137</v>
@@ -2326,13 +2326,13 @@
         <v>26.0562</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1517999999999999</v>
+        <v>-0.1520000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.01960000000000006</v>
+        <v>-0.01960000000000012</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1324000000000001</v>
+        <v>-0.1325</v>
       </c>
       <c r="V24" t="n">
         <v>-4.625900000000001</v>
